--- a/Team-Data/2012-13/4-6-2012-13.xlsx
+++ b/Team-Data/2012-13/4-6-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
         <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.538</v>
+        <v>0.545</v>
       </c>
       <c r="H2" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J2" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="N2" t="n">
         <v>0.376</v>
       </c>
       <c r="O2" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="P2" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.71</v>
+        <v>0.707</v>
       </c>
       <c r="R2" t="n">
         <v>9.1</v>
@@ -724,13 +791,13 @@
         <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
         <v>97.59999999999999</v>
@@ -763,10 +830,10 @@
         <v>6</v>
       </c>
       <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="n">
         <v>4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>5</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>15</v>
@@ -802,10 +869,10 @@
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
         <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>0.579</v>
+        <v>0.573</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1049,16 +1116,16 @@
         <v>0.448</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M4" t="n">
         <v>21.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O4" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P4" t="n">
         <v>23.8</v>
@@ -1067,19 +1134,19 @@
         <v>0.734</v>
       </c>
       <c r="R4" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S4" t="n">
         <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
@@ -1094,25 +1161,25 @@
         <v>18.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>8</v>
@@ -1124,7 +1191,7 @@
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1136,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1148,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1166,7 +1233,7 @@
         <v>17</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
         <v>4</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
         <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>0.234</v>
+        <v>0.237</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1228,19 +1295,19 @@
         <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N5" t="n">
         <v>0.334</v>
       </c>
       <c r="O5" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P5" t="n">
         <v>25.4</v>
@@ -1249,19 +1316,19 @@
         <v>0.749</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S5" t="n">
         <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U5" t="n">
         <v>19.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.3</v>
@@ -1276,7 +1343,7 @@
         <v>19.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
         <v>93.3</v>
@@ -1285,19 +1352,19 @@
         <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1321,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="AP5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ5" t="n">
         <v>19</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>12</v>
@@ -1476,7 +1543,7 @@
         <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1488,7 +1555,7 @@
         <v>13</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG7" t="n">
         <v>27</v>
@@ -1721,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M9" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O9" t="n">
         <v>18.3</v>
       </c>
       <c r="P9" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.698</v>
+        <v>0.699</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
       </c>
       <c r="S9" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T9" t="n">
         <v>44.7</v>
       </c>
       <c r="U9" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="V9" t="n">
         <v>15.1</v>
@@ -2007,13 +2074,13 @@
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.9</v>
+        <v>105.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
@@ -2037,7 +2104,7 @@
         <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2079,16 +2146,16 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -2117,34 +2184,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
         <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.325</v>
+        <v>0.329</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J10" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N10" t="n">
         <v>0.354</v>
@@ -2171,10 +2238,10 @@
         <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X10" t="n">
         <v>5</v>
@@ -2183,19 +2250,19 @@
         <v>5.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA10" t="n">
         <v>19.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="AC10" t="n">
         <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
@@ -2207,16 +2274,16 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>24</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2240,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2249,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2389,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2425,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
@@ -2440,7 +2507,7 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
         <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2508,37 +2575,37 @@
         <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
         <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
         <v>43.3</v>
       </c>
       <c r="U12" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X12" t="n">
         <v>4.1</v>
@@ -2550,25 +2617,25 @@
         <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.2</v>
+        <v>106.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF12" t="n">
         <v>11</v>
       </c>
-      <c r="AF12" t="n">
-        <v>12</v>
-      </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
         <v>24</v>
@@ -2595,7 +2662,7 @@
         <v>2</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
@@ -2616,10 +2683,10 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,7 +2695,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
         <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.623</v>
+        <v>0.632</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,10 +2748,10 @@
         <v>35.2</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
@@ -2693,19 +2760,19 @@
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
         <v>17.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
         <v>33.2</v>
@@ -2723,25 +2790,25 @@
         <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
         <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2762,7 +2829,7 @@
         <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>16</v>
@@ -2774,10 +2841,10 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
@@ -2786,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2798,7 +2865,7 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
@@ -2807,16 +2874,16 @@
         <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2959,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
         <v>26</v>
@@ -2971,7 +3038,7 @@
         <v>22</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -3105,19 +3172,19 @@
         <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
         <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
@@ -3129,7 +3196,7 @@
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>3</v>
@@ -3150,7 +3217,7 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>2</v>
@@ -3159,19 +3226,19 @@
         <v>17</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
         <v>5</v>
@@ -3299,16 +3366,16 @@
         <v>5</v>
       </c>
       <c r="AH16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>16</v>
       </c>
-      <c r="AI16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>17</v>
-      </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3323,7 +3390,7 @@
         <v>19</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>6</v>
@@ -3335,7 +3402,7 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3421,25 +3488,25 @@
         <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.397</v>
+        <v>0.394</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="U17" t="n">
         <v>22.9</v>
@@ -3448,7 +3515,7 @@
         <v>13.7</v>
       </c>
       <c r="W17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X17" t="n">
         <v>5.3</v>
@@ -3457,19 +3524,19 @@
         <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
         <v>102.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3502,25 +3569,25 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP17" t="n">
         <v>11</v>
       </c>
-      <c r="AP17" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -3573,73 +3640,73 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
         <v>39</v>
       </c>
       <c r="G18" t="n">
-        <v>0.487</v>
+        <v>0.48</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J18" t="n">
-        <v>87.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L18" t="n">
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q18" t="n">
         <v>0.741</v>
       </c>
       <c r="R18" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S18" t="n">
         <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V18" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="W18" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y18" t="n">
         <v>4.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
         <v>19.3</v>
@@ -3648,22 +3715,22 @@
         <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF18" t="n">
         <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>6</v>
@@ -3702,7 +3769,7 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>47</v>
       </c>
       <c r="G19" t="n">
-        <v>0.382</v>
+        <v>0.373</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3785,22 +3852,22 @@
         <v>17.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="O19" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P19" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
       </c>
       <c r="S19" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T19" t="n">
         <v>42.3</v>
@@ -3812,7 +3879,7 @@
         <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>4.8</v>
@@ -3821,37 +3888,37 @@
         <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3872,7 +3939,7 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -3881,7 +3948,7 @@
         <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>16</v>
@@ -3890,16 +3957,16 @@
         <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
         <v>7</v>
@@ -4215,7 +4282,7 @@
         <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
         <v>18</v>
@@ -4236,10 +4303,10 @@
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4379,16 +4446,16 @@
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>12</v>
@@ -4451,7 +4518,7 @@
         <v>8</v>
       </c>
       <c r="BB22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,7 +4640,7 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>10</v>
@@ -4582,10 +4649,10 @@
         <v>5</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>18</v>
@@ -4612,7 +4679,7 @@
         <v>11</v>
       </c>
       <c r="AU23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
         <v>11</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G24" t="n">
-        <v>0.408</v>
+        <v>0.413</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4686,16 +4753,16 @@
         <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
         <v>12.1</v>
@@ -4716,7 +4783,7 @@
         <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V24" t="n">
         <v>13.1</v>
@@ -4725,25 +4792,25 @@
         <v>7.4</v>
       </c>
       <c r="X24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AA24" t="n">
         <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.4</v>
+        <v>-3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4758,13 +4825,13 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4794,7 +4861,7 @@
         <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4803,19 +4870,19 @@
         <v>18</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4937,7 +5004,7 @@
         <v>28</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -4991,13 +5058,13 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>17</v>
@@ -5131,10 +5198,10 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>20</v>
@@ -5149,16 +5216,16 @@
         <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
         <v>16</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV26" t="n">
         <v>14</v>
@@ -5170,7 +5237,7 @@
         <v>24</v>
       </c>
       <c r="AY26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5325,7 +5392,7 @@
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
@@ -5349,7 +5416,7 @@
         <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5393,22 +5460,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F28" t="n">
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J28" t="n">
         <v>81.09999999999999</v>
@@ -5417,22 +5484,22 @@
         <v>0.484</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
         <v>8.1</v>
@@ -5441,7 +5508,7 @@
         <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U28" t="n">
         <v>25.1</v>
@@ -5450,10 +5517,10 @@
         <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>4.9</v>
@@ -5462,16 +5529,16 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB28" t="n">
         <v>103.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5489,13 +5556,13 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5519,13 +5586,13 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5534,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E29" t="n">
         <v>29</v>
       </c>
       <c r="F29" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G29" t="n">
-        <v>0.377</v>
+        <v>0.382</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5596,13 +5663,13 @@
         <v>81.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M29" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.339</v>
@@ -5611,10 +5678,10 @@
         <v>17.3</v>
       </c>
       <c r="P29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R29" t="n">
         <v>10.8</v>
@@ -5629,7 +5696,7 @@
         <v>21.5</v>
       </c>
       <c r="V29" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W29" t="n">
         <v>7.3</v>
@@ -5638,37 +5705,37 @@
         <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z29" t="n">
         <v>22.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ29" t="n">
         <v>14</v>
@@ -5695,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
         <v>27</v>
@@ -5710,13 +5777,13 @@
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5725,10 +5792,10 @@
         <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>14</v>
@@ -5847,10 +5914,10 @@
         <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
@@ -5871,7 +5938,7 @@
         <v>7</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ30" t="n">
         <v>13</v>
@@ -5889,10 +5956,10 @@
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F31" t="n">
         <v>47</v>
       </c>
       <c r="G31" t="n">
-        <v>0.382</v>
+        <v>0.373</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
@@ -5963,25 +6030,25 @@
         <v>0.433</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="N31" t="n">
         <v>0.364</v>
       </c>
       <c r="O31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S31" t="n">
         <v>32.6</v>
@@ -5993,7 +6060,7 @@
         <v>21.8</v>
       </c>
       <c r="V31" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
         <v>7.2</v>
@@ -6005,28 +6072,28 @@
         <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA31" t="n">
         <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AE31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF31" t="n">
         <v>21</v>
       </c>
       <c r="AG31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH31" t="n">
         <v>8</v>
@@ -6056,10 +6123,10 @@
         <v>18</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
         <v>6</v>
@@ -6068,10 +6135,10 @@
         <v>7</v>
       </c>
       <c r="AU31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AW31" t="n">
         <v>22</v>
@@ -6089,10 +6156,10 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-6-2012-13</t>
+          <t>2013-04-06</t>
         </is>
       </c>
     </row>
